--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Restauration légère possible (sans conduit)</t>
+          <t>Extraction / vraie restauration possible · Restauration légère possible (sans conduit)</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 122 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 179 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>aucune</t>
+          <t>surface_a_ventiler</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>66/100</t>
+          <t>61/100</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Extraction / vraie restauration possible · Restauration légère possible (sans conduit)</t>
+          <t>Restauration légère possible (sans conduit)</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
+++ b/docs/dossiers/dossier-rueil-malmaison-131bb374.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
